--- a/StructureDefinition-HivHcvViralLoadTestD.xlsx
+++ b/StructureDefinition-HivHcvViralLoadTestD.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T15:35:56+00:00</t>
+    <t>2025-01-13T20:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
